--- a/AtchisonRegime/Outputs/USA/USA500/df_regEquityReturns_USA500.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500/df_regEquityReturns_USA500.xlsx
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q696"/>
+  <dimension ref="A1:Q697"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -39517,7 +39517,7 @@
         <v>-1.113652454430497</v>
       </c>
       <c r="C686" t="n">
-        <v>0.006266379198084816</v>
+        <v>-0.01570867082860625</v>
       </c>
       <c r="D686" t="b">
         <v>0</v>
@@ -39574,7 +39574,7 @@
         <v>-1.13653593688915</v>
       </c>
       <c r="C687" t="n">
-        <v>0.02240605369896704</v>
+        <v>0.005131485533573125</v>
       </c>
       <c r="D687" t="b">
         <v>0</v>
@@ -39631,7 +39631,7 @@
         <v>-1.151360964367</v>
       </c>
       <c r="C688" t="n">
-        <v>0.05890779434252914</v>
+        <v>0.04460226520446691</v>
       </c>
       <c r="D688" t="b">
         <v>0</v>
@@ -39688,7 +39688,7 @@
         <v>-1.199054339561413</v>
       </c>
       <c r="C689" t="n">
-        <v>0.1365357185829741</v>
+        <v>0.10691331821946</v>
       </c>
       <c r="D689" t="b">
         <v>0</v>
@@ -39745,7 +39745,7 @@
         <v>-1.211312601852137</v>
       </c>
       <c r="C690" t="n">
-        <v>0.19626538484902</v>
+        <v>0.1742576329953394</v>
       </c>
       <c r="D690" t="b">
         <v>0</v>
@@ -39802,7 +39802,7 @@
         <v>-1.189056899431358</v>
       </c>
       <c r="C691" t="n">
-        <v>0.2479141243562677</v>
+        <v>0.2230893786343014</v>
       </c>
       <c r="D691" t="b">
         <v>0</v>
@@ -39859,7 +39859,7 @@
         <v>-1.098247223033612</v>
       </c>
       <c r="C692" t="n">
-        <v>0.2597235153389927</v>
+        <v>0.2419933628466199</v>
       </c>
       <c r="D692" t="b">
         <v>0</v>
@@ -39916,7 +39916,7 @@
         <v>-0.9817076186491491</v>
       </c>
       <c r="C693" t="n">
-        <v>0.2098083315261438</v>
+        <v>0.2090047006632499</v>
       </c>
       <c r="D693" t="b">
         <v>0</v>
@@ -39973,7 +39973,7 @@
         <v>-0.8763018590939128</v>
       </c>
       <c r="C694" t="n">
-        <v>0.1536160686024298</v>
+        <v>0.1277646818410845</v>
       </c>
       <c r="D694" t="b">
         <v>0</v>
@@ -40027,10 +40027,10 @@
         <v>45716</v>
       </c>
       <c r="B695" t="n">
-        <v>-0.8167702922088305</v>
+        <v>-0.8165764810113098</v>
       </c>
       <c r="C695" t="n">
-        <v>0.04657800836005581</v>
+        <v>0.03018097094312175</v>
       </c>
       <c r="D695" t="b">
         <v>0</v>
@@ -40084,10 +40084,10 @@
         <v>45747</v>
       </c>
       <c r="B696" t="n">
-        <v>-0.7844280456827043</v>
+        <v>-0.836774216411349</v>
       </c>
       <c r="C696" t="n">
-        <v>0</v>
+        <v>-0.04969816765883398</v>
       </c>
       <c r="D696" t="b">
         <v>0</v>
@@ -40133,6 +40133,63 @@
         <v>2652.864845479853</v>
       </c>
       <c r="Q696" t="n">
+        <v>278.8166411603501</v>
+      </c>
+    </row>
+    <row r="697">
+      <c r="A697" s="2" t="n">
+        <v>45777</v>
+      </c>
+      <c r="B697" t="n">
+        <v>-0.879407738343786</v>
+      </c>
+      <c r="C697" t="n">
+        <v>-0.07980487945422567</v>
+      </c>
+      <c r="D697" t="b">
+        <v>0</v>
+      </c>
+      <c r="E697" t="b">
+        <v>1</v>
+      </c>
+      <c r="F697" t="n">
+        <v>-1.03916032741589</v>
+      </c>
+      <c r="G697" t="n">
+        <v>29845950.55070484</v>
+      </c>
+      <c r="H697" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="I697" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="J697" t="n">
+        <v>0</v>
+      </c>
+      <c r="K697" t="n">
+        <v>0</v>
+      </c>
+      <c r="L697" t="n">
+        <v>-1.03916032741589</v>
+      </c>
+      <c r="M697" t="n">
+        <v>0</v>
+      </c>
+      <c r="N697" t="n">
+        <v>598.8102026084118</v>
+      </c>
+      <c r="O697" t="n">
+        <v>66.71958563839446</v>
+      </c>
+      <c r="P697" t="n">
+        <v>2625.297326465663</v>
+      </c>
+      <c r="Q697" t="n">
         <v>278.8166411603501</v>
       </c>
     </row>

--- a/AtchisonRegime/Outputs/USA/USA500/df_regEquityReturns_USA500.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500/df_regEquityReturns_USA500.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA698"/>
+  <dimension ref="A1:AA699"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60257,7 +60257,7 @@
         <v>-1.151360964367</v>
       </c>
       <c r="D688" t="n">
-        <v>0.04556975254307176</v>
+        <v>-0.05308453772626753</v>
       </c>
       <c r="E688" t="b">
         <v>0</v>
@@ -60344,7 +60344,7 @@
         <v>-1.199054339561413</v>
       </c>
       <c r="D689" t="n">
-        <v>0.1052335655208562</v>
+        <v>0.0994786913169827</v>
       </c>
       <c r="E689" t="b">
         <v>0</v>
@@ -60431,7 +60431,7 @@
         <v>-1.211312601852137</v>
       </c>
       <c r="D690" t="n">
-        <v>0.1728209275757697</v>
+        <v>0.1578384480173436</v>
       </c>
       <c r="E690" t="b">
         <v>0</v>
@@ -60518,7 +60518,7 @@
         <v>-1.189056899431358</v>
       </c>
       <c r="D691" t="n">
-        <v>0.2184151007630489</v>
+        <v>0.1952250955118413</v>
       </c>
       <c r="E691" t="b">
         <v>0</v>
@@ -60605,7 +60605,7 @@
         <v>-1.098247223033612</v>
       </c>
       <c r="D692" t="n">
-        <v>0.2303545000567671</v>
+        <v>0.2218361370592049</v>
       </c>
       <c r="E692" t="b">
         <v>0</v>
@@ -60692,7 +60692,7 @@
         <v>-0.9817076186491491</v>
       </c>
       <c r="D693" t="n">
-        <v>0.1835149024713215</v>
+        <v>0.1720865300651815</v>
       </c>
       <c r="E693" t="b">
         <v>0</v>
@@ -60779,7 +60779,7 @@
         <v>-0.8763018590939128</v>
       </c>
       <c r="D694" t="n">
-        <v>0.08173255609690118</v>
+        <v>0.08226213606388882</v>
       </c>
       <c r="E694" t="b">
         <v>0</v>
@@ -60866,7 +60866,7 @@
         <v>-0.8165764810113098</v>
       </c>
       <c r="D695" t="n">
-        <v>-0.0287673040728554</v>
+        <v>-0.01714362521200617</v>
       </c>
       <c r="E695" t="b">
         <v>0</v>
@@ -60953,7 +60953,7 @@
         <v>-0.836774216411349</v>
       </c>
       <c r="D696" t="n">
-        <v>-0.1130750000232564</v>
+        <v>-0.05274704393562812</v>
       </c>
       <c r="E696" t="b">
         <v>0</v>
@@ -61040,7 +61040,7 @@
         <v>-0.8897447119737403</v>
       </c>
       <c r="D697" t="n">
-        <v>-0.1320340448907042</v>
+        <v>-0.0352985940476525</v>
       </c>
       <c r="E697" t="b">
         <v>0</v>
@@ -61049,10 +61049,10 @@
         <v>0</v>
       </c>
       <c r="G697" t="n">
-        <v>-3.29503921298769</v>
+        <v>-2.92395629121986</v>
       </c>
       <c r="H697" t="n">
-        <v>29165592.03828806</v>
+        <v>29277508.25251923</v>
       </c>
       <c r="I697" t="inlineStr">
         <is>
@@ -61074,7 +61074,7 @@
         <v>0</v>
       </c>
       <c r="N697" t="n">
-        <v>-3.29503921298769</v>
+        <v>-2.92395629121986</v>
       </c>
       <c r="O697" t="n">
         <v>598.8102026084118</v>
@@ -61086,7 +61086,7 @@
         <v>2652.864845479853</v>
       </c>
       <c r="R697" t="n">
-        <v>269.6295235017814</v>
+        <v>270.6641644401741</v>
       </c>
       <c r="S697" t="n">
         <v>1</v>
@@ -61110,10 +61110,10 @@
         <v>0</v>
       </c>
       <c r="Z697" t="n">
-        <v>-3.29503921298769</v>
+        <v>-2.92395629121986</v>
       </c>
       <c r="AA697" t="n">
-        <v>-3.295039212987694</v>
+        <v>-2.923956291219865</v>
       </c>
     </row>
     <row r="698">
@@ -61127,7 +61127,7 @@
         <v>-0.92790417568146</v>
       </c>
       <c r="D698" t="n">
-        <v>-0.07173289590007452</v>
+        <v>0.0692095874542254</v>
       </c>
       <c r="E698" t="b">
         <v>0</v>
@@ -61136,10 +61136,10 @@
         <v>0</v>
       </c>
       <c r="G698" t="n">
-        <v>5.64090165380499</v>
+        <v>8.793936915663391</v>
       </c>
       <c r="H698" t="n">
-        <v>30810794.40191787</v>
+        <v>31852153.85872392</v>
       </c>
       <c r="I698" t="inlineStr">
         <is>
@@ -61161,7 +61161,7 @@
         <v>0</v>
       </c>
       <c r="N698" t="n">
-        <v>5.64090165380499</v>
+        <v>8.793936915663391</v>
       </c>
       <c r="O698" t="n">
         <v>598.8102026084118</v>
@@ -61173,7 +61173,7 @@
         <v>2652.864845479853</v>
       </c>
       <c r="R698" t="n">
-        <v>284.8390597521399</v>
+        <v>294.4662003143504</v>
       </c>
       <c r="S698" t="n">
         <v>2</v>
@@ -61197,10 +61197,97 @@
         <v>0</v>
       </c>
       <c r="Z698" t="n">
-        <v>5.64090165380499</v>
+        <v>8.793936915663391</v>
       </c>
       <c r="AA698" t="n">
-        <v>2.159992519358367</v>
+        <v>5.612849752752092</v>
+      </c>
+    </row>
+    <row r="699">
+      <c r="A699" s="1" t="n">
+        <v>697</v>
+      </c>
+      <c r="B699" s="2" t="n">
+        <v>45838</v>
+      </c>
+      <c r="C699" t="n">
+        <v>-0.9151477448940367</v>
+      </c>
+      <c r="D699" t="n">
+        <v>0.1501696003153849</v>
+      </c>
+      <c r="E699" t="b">
+        <v>0</v>
+      </c>
+      <c r="F699" t="b">
+        <v>0</v>
+      </c>
+      <c r="G699" t="n">
+        <v>8.793936915663391</v>
+      </c>
+      <c r="H699" t="n">
+        <v>34653212.17534014</v>
+      </c>
+      <c r="I699" t="inlineStr">
+        <is>
+          <t>Type 3: Weakening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="J699" t="inlineStr">
+        <is>
+          <t>Type 3</t>
+        </is>
+      </c>
+      <c r="K699" t="n">
+        <v>0</v>
+      </c>
+      <c r="L699" t="n">
+        <v>0</v>
+      </c>
+      <c r="M699" t="n">
+        <v>0</v>
+      </c>
+      <c r="N699" t="n">
+        <v>8.793936915663391</v>
+      </c>
+      <c r="O699" t="n">
+        <v>598.8102026084118</v>
+      </c>
+      <c r="P699" t="n">
+        <v>66.71958563839446</v>
+      </c>
+      <c r="Q699" t="n">
+        <v>2652.864845479853</v>
+      </c>
+      <c r="R699" t="n">
+        <v>320.3613722079454</v>
+      </c>
+      <c r="S699" t="n">
+        <v>3</v>
+      </c>
+      <c r="T699" t="n">
+        <v>0</v>
+      </c>
+      <c r="U699" t="n">
+        <v>0</v>
+      </c>
+      <c r="V699" t="n">
+        <v>0</v>
+      </c>
+      <c r="W699" t="n">
+        <v>0</v>
+      </c>
+      <c r="X699" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y699" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z699" t="n">
+        <v>8.793936915663391</v>
+      </c>
+      <c r="AA699" t="n">
+        <v>14.90037713484347</v>
       </c>
     </row>
   </sheetData>
@@ -61484,13 +61571,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C7C5162B-77CE-42BD-A88E-9FB2C67A3F0D}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B809AE9-7697-4898-A5E9-27657EB94735}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{411946FA-923C-4B36-896F-9E380865ED59}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAA0E930-6A64-4ABD-9A89-C994698E9DD0}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A320C30C-B2FA-4692-942F-60A0FD3A2A8A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2621F1A5-E790-4382-9FA3-FD0AED9B112C}"/>
 </file>
--- a/AtchisonRegime/Outputs/USA/USA500/df_regEquityReturns_USA500.xlsx
+++ b/AtchisonRegime/Outputs/USA/USA500/df_regEquityReturns_USA500.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA699"/>
+  <dimension ref="A1:AA702"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60344,7 +60344,7 @@
         <v>-1.199054339561413</v>
       </c>
       <c r="D689" t="n">
-        <v>0.0994786913169827</v>
+        <v>0.05734064607590641</v>
       </c>
       <c r="E689" t="b">
         <v>0</v>
@@ -60431,7 +60431,7 @@
         <v>-1.211312601852137</v>
       </c>
       <c r="D690" t="n">
-        <v>0.1578384480173436</v>
+        <v>0.1339068761472364</v>
       </c>
       <c r="E690" t="b">
         <v>0</v>
@@ -60518,7 +60518,7 @@
         <v>-1.189056899431358</v>
       </c>
       <c r="D691" t="n">
-        <v>0.1952250955118413</v>
+        <v>0.2044769373519747</v>
       </c>
       <c r="E691" t="b">
         <v>0</v>
@@ -60605,7 +60605,7 @@
         <v>-1.098247223033612</v>
       </c>
       <c r="D692" t="n">
-        <v>0.2218361370592049</v>
+        <v>0.2187455920969442</v>
       </c>
       <c r="E692" t="b">
         <v>0</v>
@@ -60692,7 +60692,7 @@
         <v>-0.9817076186491491</v>
       </c>
       <c r="D693" t="n">
-        <v>0.1720865300651815</v>
+        <v>0.1768205626204333</v>
       </c>
       <c r="E693" t="b">
         <v>0</v>
@@ -60779,7 +60779,7 @@
         <v>-0.8763018590939128</v>
       </c>
       <c r="D694" t="n">
-        <v>0.08226213606388882</v>
+        <v>0.08073394575470391</v>
       </c>
       <c r="E694" t="b">
         <v>0</v>
@@ -60866,7 +60866,7 @@
         <v>-0.8165764810113098</v>
       </c>
       <c r="D695" t="n">
-        <v>-0.01714362521200617</v>
+        <v>-0.02131999920992771</v>
       </c>
       <c r="E695" t="b">
         <v>0</v>
@@ -60953,7 +60953,7 @@
         <v>-0.836774216411349</v>
       </c>
       <c r="D696" t="n">
-        <v>-0.05274704393562812</v>
+        <v>-0.09131494158003906</v>
       </c>
       <c r="E696" t="b">
         <v>0</v>
@@ -61040,7 +61040,7 @@
         <v>-0.8897447119737403</v>
       </c>
       <c r="D697" t="n">
-        <v>-0.0352985940476525</v>
+        <v>-0.08636672660505716</v>
       </c>
       <c r="E697" t="b">
         <v>0</v>
@@ -61124,10 +61124,10 @@
         <v>45808</v>
       </c>
       <c r="C698" t="n">
-        <v>-0.92790417568146</v>
+        <v>-0.9219801244493988</v>
       </c>
       <c r="D698" t="n">
-        <v>0.0692095874542254</v>
+        <v>0.00433402541888157</v>
       </c>
       <c r="E698" t="b">
         <v>0</v>
@@ -61211,10 +61211,10 @@
         <v>45838</v>
       </c>
       <c r="C699" t="n">
-        <v>-0.9151477448940367</v>
+        <v>-0.8555726940035157</v>
       </c>
       <c r="D699" t="n">
-        <v>0.1501696003153849</v>
+        <v>0.07493456856087748</v>
       </c>
       <c r="E699" t="b">
         <v>0</v>
@@ -61288,6 +61288,267 @@
       </c>
       <c r="AA699" t="n">
         <v>14.90037713484347</v>
+      </c>
+    </row>
+    <row r="700">
+      <c r="A700" s="1" t="n">
+        <v>698</v>
+      </c>
+      <c r="B700" s="2" t="n">
+        <v>45869</v>
+      </c>
+      <c r="C700" t="n">
+        <v>-0.7604670143878566</v>
+      </c>
+      <c r="D700" t="n">
+        <v>0.08295756118067453</v>
+      </c>
+      <c r="E700" t="b">
+        <v>0</v>
+      </c>
+      <c r="F700" t="b">
+        <v>1</v>
+      </c>
+      <c r="G700" t="n">
+        <v>8.793936915663391</v>
+      </c>
+      <c r="H700" t="n">
+        <v>37700593.79329053</v>
+      </c>
+      <c r="I700" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="J700" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="K700" t="n">
+        <v>0</v>
+      </c>
+      <c r="L700" t="n">
+        <v>0</v>
+      </c>
+      <c r="M700" t="n">
+        <v>8.793936915663391</v>
+      </c>
+      <c r="N700" t="n">
+        <v>0</v>
+      </c>
+      <c r="O700" t="n">
+        <v>598.8102026084118</v>
+      </c>
+      <c r="P700" t="n">
+        <v>66.71958563839446</v>
+      </c>
+      <c r="Q700" t="n">
+        <v>2886.156106449162</v>
+      </c>
+      <c r="R700" t="n">
+        <v>320.3613722079454</v>
+      </c>
+      <c r="S700" t="n">
+        <v>1</v>
+      </c>
+      <c r="T700" t="n">
+        <v>0</v>
+      </c>
+      <c r="U700" t="n">
+        <v>0</v>
+      </c>
+      <c r="V700" t="n">
+        <v>0</v>
+      </c>
+      <c r="W700" t="n">
+        <v>0</v>
+      </c>
+      <c r="X700" t="n">
+        <v>8.793936915663391</v>
+      </c>
+      <c r="Y700" t="n">
+        <v>8.793936915663391</v>
+      </c>
+      <c r="Z700" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA700" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="701">
+      <c r="A701" s="1" t="n">
+        <v>699</v>
+      </c>
+      <c r="B701" s="2" t="n">
+        <v>45900</v>
+      </c>
+      <c r="C701" t="n">
+        <v>-0.6264616369049143</v>
+      </c>
+      <c r="D701" t="n">
+        <v>0.0646752787274633</v>
+      </c>
+      <c r="E701" t="b">
+        <v>0</v>
+      </c>
+      <c r="F701" t="b">
+        <v>1</v>
+      </c>
+      <c r="G701" t="n">
+        <v>8.793936915663391</v>
+      </c>
+      <c r="H701" t="n">
+        <v>41015960.22830301</v>
+      </c>
+      <c r="I701" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="J701" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="K701" t="n">
+        <v>0</v>
+      </c>
+      <c r="L701" t="n">
+        <v>0</v>
+      </c>
+      <c r="M701" t="n">
+        <v>8.793936915663391</v>
+      </c>
+      <c r="N701" t="n">
+        <v>0</v>
+      </c>
+      <c r="O701" t="n">
+        <v>598.8102026084118</v>
+      </c>
+      <c r="P701" t="n">
+        <v>66.71958563839446</v>
+      </c>
+      <c r="Q701" t="n">
+        <v>3139.962853737868</v>
+      </c>
+      <c r="R701" t="n">
+        <v>320.3613722079454</v>
+      </c>
+      <c r="S701" t="n">
+        <v>2</v>
+      </c>
+      <c r="T701" t="n">
+        <v>0</v>
+      </c>
+      <c r="U701" t="n">
+        <v>0</v>
+      </c>
+      <c r="V701" t="n">
+        <v>0</v>
+      </c>
+      <c r="W701" t="n">
+        <v>0</v>
+      </c>
+      <c r="X701" t="n">
+        <v>8.793936915663391</v>
+      </c>
+      <c r="Y701" t="n">
+        <v>18.36120709609346</v>
+      </c>
+      <c r="Z701" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA701" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="702">
+      <c r="A702" s="1" t="n">
+        <v>700</v>
+      </c>
+      <c r="B702" s="2" t="n">
+        <v>45930</v>
+      </c>
+      <c r="C702" t="n">
+        <v>-0.5470797216326779</v>
+      </c>
+      <c r="D702" t="n">
+        <v>0.05674426346513629</v>
+      </c>
+      <c r="E702" t="b">
+        <v>0</v>
+      </c>
+      <c r="F702" t="b">
+        <v>1</v>
+      </c>
+      <c r="G702" t="n">
+        <v>8.793936915663391</v>
+      </c>
+      <c r="H702" t="n">
+        <v>44622877.89613356</v>
+      </c>
+      <c r="I702" t="inlineStr">
+        <is>
+          <t>Type 1: Strengthening CLI &amp; Falling Inflation</t>
+        </is>
+      </c>
+      <c r="J702" t="inlineStr">
+        <is>
+          <t>Type 1</t>
+        </is>
+      </c>
+      <c r="K702" t="n">
+        <v>0</v>
+      </c>
+      <c r="L702" t="n">
+        <v>0</v>
+      </c>
+      <c r="M702" t="n">
+        <v>8.793936915663391</v>
+      </c>
+      <c r="N702" t="n">
+        <v>0</v>
+      </c>
+      <c r="O702" t="n">
+        <v>598.8102026084118</v>
+      </c>
+      <c r="P702" t="n">
+        <v>66.71958563839446</v>
+      </c>
+      <c r="Q702" t="n">
+        <v>3416.08920627084</v>
+      </c>
+      <c r="R702" t="n">
+        <v>320.3613722079454</v>
+      </c>
+      <c r="S702" t="n">
+        <v>3</v>
+      </c>
+      <c r="T702" t="n">
+        <v>0</v>
+      </c>
+      <c r="U702" t="n">
+        <v>0</v>
+      </c>
+      <c r="V702" t="n">
+        <v>0</v>
+      </c>
+      <c r="W702" t="n">
+        <v>0</v>
+      </c>
+      <c r="X702" t="n">
+        <v>8.793936915663391</v>
+      </c>
+      <c r="Y702" t="n">
+        <v>28.76981698074161</v>
+      </c>
+      <c r="Z702" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA702" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -61571,13 +61832,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{5B809AE9-7697-4898-A5E9-27657EB94735}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{59515A3D-7B8E-4C0C-B863-24FF9D9F3C86}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{BAA0E930-6A64-4ABD-9A89-C994698E9DD0}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{EB62E8B0-B15B-4377-9C04-F6CD91AD051E}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{2621F1A5-E790-4382-9FA3-FD0AED9B112C}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C9941F75-3E41-4A23-B434-1CC0AA4328EA}"/>
 </file>